--- a/schema/organizzaione-argomenti.xlsx
+++ b/schema/organizzaione-argomenti.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ottavia\Documents\GitHub\test-organizzioni-fisppa\schema\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tita/test-organizzioni-fisppa/schema/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FD6C66-08EF-4825-A9C6-0FBB1229202C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B3B055-89FF-B84C-951E-438D0130C7EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9E034456-4125-47B2-8B99-8ECE4D8D9548}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17720" xr2:uid="{9E034456-4125-47B2-8B99-8ECE4D8D9548}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="24">
   <si>
     <t>Parte</t>
   </si>
@@ -44,33 +44,21 @@
     <t>Argomento</t>
   </si>
   <si>
-    <t>Numero lezioni</t>
-  </si>
-  <si>
     <t>Docente/Note</t>
   </si>
   <si>
     <t>Parte I</t>
   </si>
   <si>
-    <t>Concetto di misura</t>
-  </si>
-  <si>
     <t>Ottavia</t>
   </si>
   <si>
-    <t>Scale di misura (indici di tendenza centrale, frequenze)</t>
-  </si>
-  <si>
     <t>Introduzione a R</t>
   </si>
   <si>
     <t>Concetti di statistica di base (dispersione, skewness, kurtosis, IQR, sd, var)</t>
   </si>
   <si>
-    <t>Marghe + grafici</t>
-  </si>
-  <si>
     <t>Parte II</t>
   </si>
   <si>
@@ -87,15 +75,6 @@
   </si>
   <si>
     <t>Modelli di misura – EFA: applicazione</t>
-  </si>
-  <si>
-    <t>Margherita</t>
-  </si>
-  <si>
-    <t>Test nelle organizzazioni</t>
-  </si>
-  <si>
-    <t>Possibili ospiti (Luca?, Enrico Perinelli?)</t>
   </si>
   <si>
     <r>
@@ -136,10 +115,19 @@
     <t>Ripasso per esame</t>
   </si>
   <si>
-    <t>Parte III</t>
-  </si>
-  <si>
     <t xml:space="preserve">Marghe </t>
+  </si>
+  <si>
+    <t>Probabilità, la distribuzione Normale e i punteggi standardizzati</t>
+  </si>
+  <si>
+    <t>Concetto di misura, Scale di misura (indici di tendenza centrale, frequenze)</t>
+  </si>
+  <si>
+    <t>Numero ore</t>
+  </si>
+  <si>
+    <t>Otta Marghe</t>
   </si>
 </sst>
 </file>
@@ -183,12 +171,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -204,7 +193,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -521,14 +510,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{287D4B79-B5EA-4809-8D60-39C024664462}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="62.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.453125" customWidth="1"/>
-    <col min="5" max="5" width="21.81640625" customWidth="1"/>
+    <col min="2" max="2" width="56.33203125" customWidth="1"/>
+    <col min="3" max="3" width="14.5" customWidth="1"/>
+    <col min="5" max="5" width="21.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -536,249 +525,238 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" s="1">
         <v>46076</v>
       </c>
       <c r="F2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1">
+        <v>46083</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1">
+        <v>46090</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1">
+        <v>46097</v>
+      </c>
+      <c r="F5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1">
-        <v>46076</v>
-      </c>
-      <c r="F3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1">
+        <v>46104</v>
+      </c>
+      <c r="F6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1">
+        <v>46111</v>
+      </c>
+      <c r="F7" t="s">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4" s="1">
-        <v>46083</v>
-      </c>
-      <c r="F4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1">
+        <v>46125</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1">
+        <v>46132</v>
+      </c>
+      <c r="F9" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5" s="1">
-        <v>46090</v>
-      </c>
-      <c r="F5" t="s">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1">
+        <v>46139</v>
+      </c>
+      <c r="F10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1">
-        <v>46097</v>
-      </c>
-      <c r="F6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1">
-        <v>46104</v>
-      </c>
-      <c r="F7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8" s="1">
-        <v>46111</v>
-      </c>
-      <c r="F8" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1">
+        <v>46146</v>
+      </c>
+      <c r="F11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
         <v>15</v>
       </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9" s="1">
-        <v>46125</v>
-      </c>
-      <c r="F9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1">
+        <v>46153</v>
+      </c>
+      <c r="F12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
         <v>16</v>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10" s="1">
-        <v>46132</v>
-      </c>
-      <c r="F10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11" s="1">
-        <v>46139</v>
-      </c>
-      <c r="F11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12" s="1">
-        <v>46146</v>
-      </c>
-      <c r="F12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
       <c r="C13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="F13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
         <v>18</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" s="1">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="F14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15" s="1">
-        <v>46167</v>
-      </c>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D15" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/schema/organizzaione-argomenti.xlsx
+++ b/schema/organizzaione-argomenti.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tita/test-organizzioni-fisppa/schema/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B3B055-89FF-B84C-951E-438D0130C7EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6DB634A-EB84-6243-8405-7CE9B8124752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17720" xr2:uid="{9E034456-4125-47B2-8B99-8ECE4D8D9548}"/>
   </bookViews>
@@ -62,12 +62,6 @@
     <t>Parte II</t>
   </si>
   <si>
-    <t>Test di prestazione tipica e massima, scale di risposta</t>
-  </si>
-  <si>
-    <t>Analisi preliminare degli item (pattern aberranti, correlazioni policoriche)</t>
-  </si>
-  <si>
     <t>Marghe</t>
   </si>
   <si>
@@ -75,6 +69,33 @@
   </si>
   <si>
     <t>Modelli di misura – EFA: applicazione</t>
+  </si>
+  <si>
+    <t>Modelli di misura – CFA: concetto e output</t>
+  </si>
+  <si>
+    <t>Modelli di misura – CFA: applicazione</t>
+  </si>
+  <si>
+    <t>giorno</t>
+  </si>
+  <si>
+    <t>Ripasso per esame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marghe </t>
+  </si>
+  <si>
+    <t>Concetto di misura, Scale di misura (indici di tendenza centrale, frequenze)</t>
+  </si>
+  <si>
+    <t>Numero ore</t>
+  </si>
+  <si>
+    <t>Otta Marghe</t>
+  </si>
+  <si>
+    <t>Analisi preliminare degli item (pattern aberranti (parla qui di dati mancanti), correlazioni policoriche)</t>
   </si>
   <si>
     <r>
@@ -86,7 +107,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Validità, attendibilità e dimensionalità</t>
+      <t>Correlazione e dimensionalità, item reverse</t>
     </r>
     <r>
       <rPr>
@@ -100,34 +121,13 @@
     </r>
   </si>
   <si>
-    <t>Modelli di misura – CFA: concetto e output</t>
-  </si>
-  <si>
-    <t>Modelli di misura – CFA: applicazione</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modelli di misura - IRT </t>
-  </si>
-  <si>
-    <t>giorno</t>
-  </si>
-  <si>
-    <t>Ripasso per esame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marghe </t>
-  </si>
-  <si>
-    <t>Probabilità, la distribuzione Normale e i punteggi standardizzati</t>
-  </si>
-  <si>
-    <t>Concetto di misura, Scale di misura (indici di tendenza centrale, frequenze)</t>
-  </si>
-  <si>
-    <t>Numero ore</t>
-  </si>
-  <si>
-    <t>Otta Marghe</t>
+    <t>Validità, attendibilità</t>
+  </si>
+  <si>
+    <t>Media SD CV (come unità di misura, per confrontare scale diverse); Punteggi standardizzati, Probabilità, la distribuzione Normale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test di prestazione tipica e massima, scale di risposta, </t>
   </si>
 </sst>
 </file>
@@ -171,10 +171,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -512,7 +511,7 @@
   <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="56.33203125" customWidth="1"/>
+    <col min="2" max="2" width="59.83203125" customWidth="1"/>
     <col min="3" max="3" width="14.5" customWidth="1"/>
     <col min="5" max="5" width="21.83203125" customWidth="1"/>
   </cols>
@@ -525,10 +524,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
@@ -538,8 +537,8 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>21</v>
+      <c r="B2" t="s">
+        <v>16</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -565,7 +564,7 @@
         <v>46083</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -582,7 +581,7 @@
         <v>46090</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -590,7 +589,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -607,7 +606,7 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -616,7 +615,7 @@
         <v>46104</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -624,7 +623,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -641,7 +640,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -650,7 +649,7 @@
         <v>46125</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -658,7 +657,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -675,7 +674,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -684,7 +683,7 @@
         <v>46139</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -692,7 +691,7 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -709,7 +708,7 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C12">
         <v>3</v>
@@ -718,7 +717,7 @@
         <v>46153</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -726,7 +725,7 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C13">
         <v>3</v>
@@ -743,7 +742,7 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C14">
         <v>3</v>
@@ -752,7 +751,7 @@
         <v>46167</v>
       </c>
       <c r="F14" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">

--- a/schema/organizzaione-argomenti.xlsx
+++ b/schema/organizzaione-argomenti.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tita/test-organizzioni-fisppa/schema/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6DB634A-EB84-6243-8405-7CE9B8124752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E55B5F07-C8BE-654E-AF70-EF8E4C2743AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17720" xr2:uid="{9E034456-4125-47B2-8B99-8ECE4D8D9548}"/>
   </bookViews>

--- a/schema/organizzaione-argomenti.xlsx
+++ b/schema/organizzaione-argomenti.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tita/test-organizzioni-fisppa/schema/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ottavia\Documents\GitHub\test-organizzioni-fisppa\schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E55B5F07-C8BE-654E-AF70-EF8E4C2743AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88179D7-CA74-47CE-8688-48C063D8BC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17720" xr2:uid="{9E034456-4125-47B2-8B99-8ECE4D8D9548}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9E034456-4125-47B2-8B99-8ECE4D8D9548}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="25">
   <si>
     <t>Parte</t>
   </si>
@@ -128,6 +128,9 @@
   </si>
   <si>
     <t xml:space="preserve">Test di prestazione tipica e massima, scale di risposta, </t>
+  </si>
+  <si>
+    <t>Marge</t>
   </si>
 </sst>
 </file>
@@ -176,7 +179,7 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -192,7 +195,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -508,15 +511,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{287D4B79-B5EA-4809-8D60-39C024664462}">
-  <dimension ref="A1:F15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="59.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.5" customWidth="1"/>
-    <col min="5" max="5" width="21.83203125" customWidth="1"/>
+    <col min="2" max="2" width="59.81640625" customWidth="1"/>
+    <col min="3" max="3" width="14.453125" customWidth="1"/>
+    <col min="5" max="5" width="21.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -533,7 +536,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -550,7 +553,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -567,7 +570,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -584,7 +587,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -601,7 +604,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -612,13 +615,13 @@
         <v>3</v>
       </c>
       <c r="D6" s="1">
-        <v>46104</v>
+        <v>46111</v>
       </c>
       <c r="F6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -629,115 +632,115 @@
         <v>3</v>
       </c>
       <c r="D7" s="1">
-        <v>46111</v>
+        <v>46125</v>
       </c>
       <c r="F7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1">
+        <v>46132</v>
+      </c>
+      <c r="F8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
         <v>19</v>
       </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1">
-        <v>46125</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1">
+        <v>46139</v>
+      </c>
+      <c r="F9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
         <v>9</v>
       </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1">
-        <v>46132</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1">
+        <v>46146</v>
+      </c>
+      <c r="F10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
         <v>10</v>
       </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1">
-        <v>46139</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1">
+        <v>46153</v>
+      </c>
+      <c r="F11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1">
+        <v>46160</v>
+      </c>
+      <c r="F12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1">
+        <v>46167</v>
+      </c>
+      <c r="F13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1">
-        <v>46146</v>
-      </c>
-      <c r="F11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1">
-        <v>46153</v>
-      </c>
-      <c r="F12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1">
-        <v>46160</v>
-      </c>
-      <c r="F13" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -754,8 +757,144 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="D15" s="1"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1">
+        <v>46125</v>
+      </c>
+      <c r="F28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1">
+        <v>46132</v>
+      </c>
+      <c r="F29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1">
+        <v>46139</v>
+      </c>
+      <c r="F30" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1">
+        <v>46146</v>
+      </c>
+      <c r="F31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1">
+        <v>46153</v>
+      </c>
+      <c r="F32" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1">
+        <v>46160</v>
+      </c>
+      <c r="F33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1">
+        <v>46167</v>
+      </c>
+      <c r="F34" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1">
+        <v>46167</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/schema/organizzaione-argomenti.xlsx
+++ b/schema/organizzaione-argomenti.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ottavia\Documents\GitHub\test-organizzioni-fisppa\schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88179D7-CA74-47CE-8688-48C063D8BC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66DF9EF-F06F-4364-80D9-9E9B271D0D70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9E034456-4125-47B2-8B99-8ECE4D8D9548}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="27">
   <si>
     <t>Parte</t>
   </si>
@@ -131,6 +131,12 @@
   </si>
   <si>
     <t>Marge</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cross validation e traduzione</t>
+  </si>
+  <si>
+    <t>Validità, attendibilità, Correlazione e dimensionalità, item reverse</t>
   </si>
 </sst>
 </file>
@@ -626,7 +632,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -643,7 +649,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C8">
         <v>3</v>

--- a/schema/organizzaione-argomenti.xlsx
+++ b/schema/organizzaione-argomenti.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ottavia\Documents\GitHub\test-organizzioni-fisppa\schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66DF9EF-F06F-4364-80D9-9E9B271D0D70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B61BF9-8594-45DA-9AF1-C8F21E3CA27D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9E034456-4125-47B2-8B99-8ECE4D8D9548}"/>
+    <workbookView xWindow="32580" yWindow="2595" windowWidth="21600" windowHeight="11175" xr2:uid="{9E034456-4125-47B2-8B99-8ECE4D8D9548}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
   <si>
     <t>Parte</t>
   </si>
@@ -133,10 +133,13 @@
     <t>Marge</t>
   </si>
   <si>
-    <t xml:space="preserve"> cross validation e traduzione</t>
-  </si>
-  <si>
-    <t>Validità, attendibilità, Correlazione e dimensionalità, item reverse</t>
+    <t>Correlazione e dimensionalità, item reverse, analisi degli item</t>
+  </si>
+  <si>
+    <t>Validità e attendibilità</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Introduzione all'analisi fattoriale cross validation e traduzione</t>
   </si>
 </sst>
 </file>
@@ -517,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{287D4B79-B5EA-4809-8D60-39C024664462}">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="59.81640625" customWidth="1"/>
@@ -632,7 +635,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -649,7 +652,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -736,11 +739,8 @@
       <c r="B13" t="s">
         <v>12</v>
       </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
       <c r="D13" s="1">
-        <v>46167</v>
+        <v>46163</v>
       </c>
       <c r="F13" t="s">
         <v>8</v>
@@ -751,7 +751,7 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C14">
         <v>3</v>
@@ -760,27 +760,18 @@
         <v>46167</v>
       </c>
       <c r="F14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="1">
+        <v>46168</v>
+      </c>
+      <c r="F15" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="D15" s="1"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>7</v>
-      </c>
-      <c r="B28" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1">
-        <v>46125</v>
-      </c>
-      <c r="F28" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -788,16 +779,16 @@
         <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C29">
         <v>3</v>
       </c>
       <c r="D29" s="1">
-        <v>46132</v>
+        <v>46125</v>
       </c>
       <c r="F29" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
@@ -805,16 +796,16 @@
         <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C30">
         <v>3</v>
       </c>
       <c r="D30" s="1">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="F30" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
@@ -822,16 +813,16 @@
         <v>7</v>
       </c>
       <c r="B31" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C31">
         <v>3</v>
       </c>
       <c r="D31" s="1">
-        <v>46146</v>
+        <v>46139</v>
       </c>
       <c r="F31" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -839,16 +830,16 @@
         <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C32">
         <v>3</v>
       </c>
       <c r="D32" s="1">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="F32" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -856,16 +847,16 @@
         <v>7</v>
       </c>
       <c r="B33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C33">
         <v>3</v>
       </c>
       <c r="D33" s="1">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="F33" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
@@ -873,16 +864,16 @@
         <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C34">
         <v>3</v>
       </c>
       <c r="D34" s="1">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="F34" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
@@ -890,7 +881,7 @@
         <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C35">
         <v>3</v>
@@ -899,6 +890,23 @@
         <v>46167</v>
       </c>
       <c r="F35" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1">
+        <v>46167</v>
+      </c>
+      <c r="F36" t="s">
         <v>18</v>
       </c>
     </row>

--- a/schema/organizzaione-argomenti.xlsx
+++ b/schema/organizzaione-argomenti.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ottavia\Documents\GitHub\test-organizzioni-fisppa\schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B61BF9-8594-45DA-9AF1-C8F21E3CA27D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DADFD3FA-D949-4A57-A2AE-644E19DF61C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32580" yWindow="2595" windowWidth="21600" windowHeight="11175" xr2:uid="{9E034456-4125-47B2-8B99-8ECE4D8D9548}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="27">
   <si>
     <t>Parte</t>
   </si>
@@ -128,9 +128,6 @@
   </si>
   <si>
     <t xml:space="preserve">Test di prestazione tipica e massima, scale di risposta, </t>
-  </si>
-  <si>
-    <t>Marge</t>
   </si>
   <si>
     <t>Correlazione e dimensionalità, item reverse, analisi degli item</t>
@@ -635,7 +632,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -652,7 +649,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -712,7 +709,7 @@
         <v>46153</v>
       </c>
       <c r="F11" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -751,7 +748,7 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14">
         <v>3</v>
